--- a/artfynd/A 698-2026 artfynd.xlsx
+++ b/artfynd/A 698-2026 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>131082418</v>
       </c>
       <c r="B4" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>131082405</v>
       </c>
       <c r="B5" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 698-2026 artfynd.xlsx
+++ b/artfynd/A 698-2026 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>131082418</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>131082405</v>
       </c>
       <c r="B5" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 698-2026 artfynd.xlsx
+++ b/artfynd/A 698-2026 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>131082418</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>131082405</v>
       </c>
       <c r="B5" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 698-2026 artfynd.xlsx
+++ b/artfynd/A 698-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1135,6 +1135,404 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131600587</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8442</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Brunstmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>572492</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6447058</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131600750</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97896</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Brunstmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>572517</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6447054</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131600604</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91847</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Brunstmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>572492</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6447058</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131600466</v>
+      </c>
+      <c r="B9" t="n">
+        <v>75364</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Brunstmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>572468</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6447027</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 698-2026 artfynd.xlsx
+++ b/artfynd/A 698-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1247,7 +1247,7 @@
         <v>131600750</v>
       </c>
       <c r="B7" t="n">
-        <v>97896</v>
+        <v>97898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>131600604</v>
       </c>
       <c r="B8" t="n">
-        <v>91847</v>
+        <v>91849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>131600466</v>
       </c>
       <c r="B9" t="n">
-        <v>75364</v>
+        <v>75366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,6 +1532,108 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131621114</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97648</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Brunstmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>572477</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6447047</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 698-2026 artfynd.xlsx
+++ b/artfynd/A 698-2026 artfynd.xlsx
@@ -1247,7 +1247,7 @@
         <v>131600750</v>
       </c>
       <c r="B7" t="n">
-        <v>97898</v>
+        <v>97899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>131621114</v>
       </c>
       <c r="B10" t="n">
-        <v>97648</v>
+        <v>97649</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 698-2026 artfynd.xlsx
+++ b/artfynd/A 698-2026 artfynd.xlsx
@@ -1140,7 +1140,7 @@
         <v>131600587</v>
       </c>
       <c r="B6" t="n">
-        <v>8442</v>
+        <v>8443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>131600750</v>
       </c>
       <c r="B7" t="n">
-        <v>97899</v>
+        <v>97900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>131600604</v>
       </c>
       <c r="B8" t="n">
-        <v>91849</v>
+        <v>91850</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>131600466</v>
       </c>
       <c r="B9" t="n">
-        <v>75366</v>
+        <v>75367</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>131621114</v>
       </c>
       <c r="B10" t="n">
-        <v>97649</v>
+        <v>97650</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 698-2026 artfynd.xlsx
+++ b/artfynd/A 698-2026 artfynd.xlsx
@@ -1247,7 +1247,7 @@
         <v>131600750</v>
       </c>
       <c r="B7" t="n">
-        <v>97900</v>
+        <v>97903</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>131600604</v>
       </c>
       <c r="B8" t="n">
-        <v>91850</v>
+        <v>91853</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>131600466</v>
       </c>
       <c r="B9" t="n">
-        <v>75367</v>
+        <v>75370</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>131621114</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
+        <v>97653</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 698-2026 artfynd.xlsx
+++ b/artfynd/A 698-2026 artfynd.xlsx
@@ -1247,7 +1247,7 @@
         <v>131600750</v>
       </c>
       <c r="B7" t="n">
-        <v>97903</v>
+        <v>97909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>131600604</v>
       </c>
       <c r="B8" t="n">
-        <v>91853</v>
+        <v>91859</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>131600466</v>
       </c>
       <c r="B9" t="n">
-        <v>75370</v>
+        <v>75372</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>131621114</v>
       </c>
       <c r="B10" t="n">
-        <v>97653</v>
+        <v>97659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 698-2026 artfynd.xlsx
+++ b/artfynd/A 698-2026 artfynd.xlsx
@@ -1140,7 +1140,7 @@
         <v>131600587</v>
       </c>
       <c r="B6" t="n">
-        <v>8443</v>
+        <v>8444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>131600750</v>
       </c>
       <c r="B7" t="n">
-        <v>97909</v>
+        <v>97912</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>131600604</v>
       </c>
       <c r="B8" t="n">
-        <v>91859</v>
+        <v>91862</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>131600466</v>
       </c>
       <c r="B9" t="n">
-        <v>75372</v>
+        <v>75375</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>131621114</v>
       </c>
       <c r="B10" t="n">
-        <v>97659</v>
+        <v>97662</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 698-2026 artfynd.xlsx
+++ b/artfynd/A 698-2026 artfynd.xlsx
@@ -1247,7 +1247,7 @@
         <v>131600750</v>
       </c>
       <c r="B7" t="n">
-        <v>97912</v>
+        <v>97917</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>131600604</v>
       </c>
       <c r="B8" t="n">
-        <v>91862</v>
+        <v>91867</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>131600466</v>
       </c>
       <c r="B9" t="n">
-        <v>75375</v>
+        <v>75380</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>131621114</v>
       </c>
       <c r="B10" t="n">
-        <v>97662</v>
+        <v>97667</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 698-2026 artfynd.xlsx
+++ b/artfynd/A 698-2026 artfynd.xlsx
@@ -1247,7 +1247,7 @@
         <v>131600750</v>
       </c>
       <c r="B7" t="n">
-        <v>97917</v>
+        <v>97919</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>131600604</v>
       </c>
       <c r="B8" t="n">
-        <v>91867</v>
+        <v>91869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>131600466</v>
       </c>
       <c r="B9" t="n">
-        <v>75380</v>
+        <v>75382</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>131621114</v>
       </c>
       <c r="B10" t="n">
-        <v>97667</v>
+        <v>97669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 698-2026 artfynd.xlsx
+++ b/artfynd/A 698-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1635,6 +1635,765 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132696800</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57946</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 698, Öjsjön,Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>572453</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6447025</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Bearbetat nedre delen av barkborregran</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132696862</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 698, Öjsjön,Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>572501</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6447042</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132696836</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 698, Öjsjön,Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>572494</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6447030</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132698650</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A 698, Öjsjön,Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>572482</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6447052</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132696760</v>
+      </c>
+      <c r="B15" t="n">
+        <v>96702</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>A 698, Öjsjön,Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>572442</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6447011</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ett 20-tal rätt stora kuddar.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132696822</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A 698, Öjsjön,Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>572465</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6447034</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132698660</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>A 698, Öjsjön,Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>572501</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6447034</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 698-2026 artfynd.xlsx
+++ b/artfynd/A 698-2026 artfynd.xlsx
@@ -1640,7 +1640,7 @@
         <v>132696800</v>
       </c>
       <c r="B11" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>132696862</v>
       </c>
       <c r="B12" t="n">
-        <v>99112</v>
+        <v>99116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1853,10 +1853,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132696836</v>
+        <v>132698650</v>
       </c>
       <c r="B13" t="n">
-        <v>99112</v>
+        <v>99116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1881,7 +1881,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1896,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572494</v>
+        <v>572482</v>
       </c>
       <c r="R13" t="n">
-        <v>6447030</v>
+        <v>6447052</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1959,10 +1963,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132698650</v>
+        <v>132696836</v>
       </c>
       <c r="B14" t="n">
-        <v>99112</v>
+        <v>99116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1987,11 +1991,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572482</v>
+        <v>572494</v>
       </c>
       <c r="R14" t="n">
-        <v>6447052</v>
+        <v>6447030</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2072,7 +2072,7 @@
         <v>132696760</v>
       </c>
       <c r="B15" t="n">
-        <v>96702</v>
+        <v>96706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2184,10 +2184,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132696822</v>
+        <v>132698660</v>
       </c>
       <c r="B16" t="n">
-        <v>99112</v>
+        <v>99116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572465</v>
+        <v>572501</v>
       </c>
       <c r="R16" t="n">
         <v>6447034</v>
@@ -2290,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132698660</v>
+        <v>132696822</v>
       </c>
       <c r="B17" t="n">
-        <v>99112</v>
+        <v>99116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572501</v>
+        <v>572465</v>
       </c>
       <c r="R17" t="n">
         <v>6447034</v>

--- a/artfynd/A 698-2026 artfynd.xlsx
+++ b/artfynd/A 698-2026 artfynd.xlsx
@@ -1750,7 +1750,7 @@
         <v>132696862</v>
       </c>
       <c r="B12" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>132698650</v>
       </c>
       <c r="B13" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>132696836</v>
       </c>
       <c r="B14" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>132696760</v>
       </c>
       <c r="B15" t="n">
-        <v>96706</v>
+        <v>96707</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>132698660</v>
       </c>
       <c r="B16" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>132696822</v>
       </c>
       <c r="B17" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 698-2026 artfynd.xlsx
+++ b/artfynd/A 698-2026 artfynd.xlsx
@@ -1750,7 +1750,7 @@
         <v>132696862</v>
       </c>
       <c r="B12" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>132698650</v>
       </c>
       <c r="B13" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1966,7 +1966,7 @@
         <v>132696836</v>
       </c>
       <c r="B14" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>132696760</v>
       </c>
       <c r="B15" t="n">
-        <v>96707</v>
+        <v>96708</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2187,7 +2187,7 @@
         <v>132698660</v>
       </c>
       <c r="B16" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2293,7 +2293,7 @@
         <v>132696822</v>
       </c>
       <c r="B17" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 698-2026 artfynd.xlsx
+++ b/artfynd/A 698-2026 artfynd.xlsx
@@ -1846,7 +1846,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 698-2026 artfynd.xlsx
+++ b/artfynd/A 698-2026 artfynd.xlsx
@@ -1846,14 +1846,14 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132698650</v>
+        <v>132696836</v>
       </c>
       <c r="B13" t="n">
         <v>99118</v>
@@ -1881,11 +1881,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1900,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572482</v>
+        <v>572494</v>
       </c>
       <c r="R13" t="n">
-        <v>6447052</v>
+        <v>6447030</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132696836</v>
+        <v>132698650</v>
       </c>
       <c r="B14" t="n">
         <v>99118</v>
@@ -1991,7 +1987,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572494</v>
+        <v>572482</v>
       </c>
       <c r="R14" t="n">
-        <v>6447030</v>
+        <v>6447052</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 698-2026 artfynd.xlsx
+++ b/artfynd/A 698-2026 artfynd.xlsx
@@ -1640,7 +1640,7 @@
         <v>132696800</v>
       </c>
       <c r="B11" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>132696862</v>
       </c>
       <c r="B12" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1853,10 +1853,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132696836</v>
+        <v>132698650</v>
       </c>
       <c r="B13" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1881,7 +1881,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1896,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572494</v>
+        <v>572482</v>
       </c>
       <c r="R13" t="n">
-        <v>6447030</v>
+        <v>6447052</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1959,10 +1963,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132698650</v>
+        <v>132696836</v>
       </c>
       <c r="B14" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1987,11 +1991,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572482</v>
+        <v>572494</v>
       </c>
       <c r="R14" t="n">
-        <v>6447052</v>
+        <v>6447030</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2072,7 +2072,7 @@
         <v>132696760</v>
       </c>
       <c r="B15" t="n">
-        <v>96708</v>
+        <v>96709</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>132698660</v>
       </c>
       <c r="B16" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>132696822</v>
       </c>
       <c r="B17" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 698-2026 artfynd.xlsx
+++ b/artfynd/A 698-2026 artfynd.xlsx
@@ -1740,7 +1740,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1750,7 +1750,7 @@
         <v>132696862</v>
       </c>
       <c r="B12" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1856,7 +1856,7 @@
         <v>132698650</v>
       </c>
       <c r="B13" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>132696836</v>
       </c>
       <c r="B14" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2072,7 +2072,7 @@
         <v>132696760</v>
       </c>
       <c r="B15" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2187,7 +2187,7 @@
         <v>132698660</v>
       </c>
       <c r="B16" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>132696822</v>
       </c>
       <c r="B17" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 698-2026 artfynd.xlsx
+++ b/artfynd/A 698-2026 artfynd.xlsx
@@ -1740,7 +1740,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1750,7 +1750,7 @@
         <v>132696862</v>
       </c>
       <c r="B12" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1856,7 +1856,7 @@
         <v>132698650</v>
       </c>
       <c r="B13" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>132696836</v>
       </c>
       <c r="B14" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2072,7 +2072,7 @@
         <v>132696760</v>
       </c>
       <c r="B15" t="n">
-        <v>96711</v>
+        <v>96712</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2187,7 +2187,7 @@
         <v>132698660</v>
       </c>
       <c r="B16" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>132696822</v>
       </c>
       <c r="B17" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 698-2026 artfynd.xlsx
+++ b/artfynd/A 698-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>109036973</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572435.0360198186</v>
+        <v>572435</v>
       </c>
       <c r="R2" t="n">
-        <v>6447022.253725315</v>
+        <v>6447023</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -801,42 +796,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130982594</v>
+        <v>132696760</v>
       </c>
       <c r="B3" t="n">
-        <v>58043</v>
+        <v>96783</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572454</v>
+        <v>572442</v>
       </c>
       <c r="R3" t="n">
-        <v>6447019</v>
+        <v>6447011</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,12 +873,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ett 20-tal rätt stora kuddar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,6 +892,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,68 +904,56 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131082418</v>
+        <v>131621114</v>
       </c>
       <c r="B4" t="n">
-        <v>57885</v>
+        <v>97810</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öjsjön-Falerum, Sm</t>
+          <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572505</v>
+        <v>572477</v>
       </c>
       <c r="R4" t="n">
-        <v>6447038</v>
+        <v>6447047</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,12 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,28 +994,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131082405</v>
+        <v>131600604</v>
       </c>
       <c r="B5" t="n">
-        <v>58047</v>
+        <v>91995</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,50 +1024,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öjsjön-Falerum, Sm</t>
+          <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572475</v>
+        <v>572492</v>
       </c>
       <c r="R5" t="n">
-        <v>6447038</v>
+        <v>6447058</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,17 +1078,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Revirparet i del av sitt revir</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,66 +1098,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131600587</v>
+        <v>131600466</v>
       </c>
       <c r="B6" t="n">
-        <v>8444</v>
+        <v>75468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572492</v>
+        <v>572468</v>
       </c>
       <c r="R6" t="n">
-        <v>6447058</v>
+        <v>6447027</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,7 +1189,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1244,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131600750</v>
+        <v>131082418</v>
       </c>
       <c r="B7" t="n">
-        <v>97919</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,34 +1218,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brunstmossen, Sm</t>
+          <t>Öjsjön-Falerum, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572517</v>
+        <v>572505</v>
       </c>
       <c r="R7" t="n">
-        <v>6447054</v>
+        <v>6447038</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,12 +1288,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,60 +1308,68 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131600604</v>
+        <v>132696800</v>
       </c>
       <c r="B8" t="n">
-        <v>91869</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Brunstmossen, Sm</t>
+          <t>A 698, Öjsjön,Falerum, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572492</v>
+        <v>572453</v>
       </c>
       <c r="R8" t="n">
-        <v>6447058</v>
+        <v>6447025</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,12 +1393,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Bearbetat nedre delen av barkborregran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,60 +1418,72 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131600466</v>
+        <v>130982543</v>
       </c>
       <c r="B9" t="n">
-        <v>75382</v>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Brunstmossen, Sm</t>
+          <t>A 698, Öjsjön, Falerum, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572468</v>
+        <v>572484</v>
       </c>
       <c r="R9" t="n">
-        <v>6447027</v>
+        <v>6446993</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1503,12 +1507,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1523,64 +1527,68 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131621114</v>
+        <v>130982594</v>
       </c>
       <c r="B10" t="n">
-        <v>97705</v>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Brunstmossen, Sm</t>
+          <t>A 698, Öjsjön,Falerum, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572477</v>
+        <v>572454</v>
       </c>
       <c r="R10" t="n">
-        <v>6447047</v>
+        <v>6447019</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1604,12 +1612,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,29 +1626,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132696800</v>
+        <v>131082405</v>
       </c>
       <c r="B11" t="n">
-        <v>57955</v>
+        <v>58114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,45 +1655,53 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 698, Öjsjön,Falerum, Sm</t>
+          <t>Öjsjön-Falerum, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572453</v>
+        <v>572475</v>
       </c>
       <c r="R11" t="n">
-        <v>6447025</v>
+        <v>6447038</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1710,17 +1725,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Bearbetat nedre delen av barkborregran</t>
+          <t>Revirparet i del av sitt revir</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,22 +1750,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132696862</v>
+        <v>131628992</v>
       </c>
       <c r="B12" t="n">
-        <v>99130</v>
+        <v>58624</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1758,42 +1773,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103042</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 698, Öjsjön,Falerum, Sm</t>
+          <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572501</v>
+        <v>572511</v>
       </c>
       <c r="R12" t="n">
-        <v>6447042</v>
+        <v>6447070</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,12 +1831,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1834,76 +1845,72 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132698650</v>
+        <v>131600587</v>
       </c>
       <c r="B13" t="n">
-        <v>99130</v>
+        <v>8449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 698, Öjsjön,Falerum, Sm</t>
+          <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572482</v>
+        <v>572492</v>
       </c>
       <c r="R13" t="n">
-        <v>6447052</v>
+        <v>6447058</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,12 +1937,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1951,22 +1958,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132696836</v>
+        <v>132696822</v>
       </c>
       <c r="B14" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2006,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572494</v>
+        <v>572465</v>
       </c>
       <c r="R14" t="n">
-        <v>6447030</v>
+        <v>6447034</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,39 +2076,35 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132696760</v>
+        <v>132696836</v>
       </c>
       <c r="B15" t="n">
-        <v>96718</v>
+        <v>99195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2116,13 +2119,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572442</v>
+        <v>572494</v>
       </c>
       <c r="R15" t="n">
-        <v>6447011</v>
+        <v>6447030</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2152,11 +2155,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ett 20-tal rätt stora kuddar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,10 +2182,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132698660</v>
+        <v>132696862</v>
       </c>
       <c r="B16" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2230,7 +2228,7 @@
         <v>572501</v>
       </c>
       <c r="R16" t="n">
-        <v>6447034</v>
+        <v>6447042</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2290,10 +2288,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132696822</v>
+        <v>132698650</v>
       </c>
       <c r="B17" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2318,7 +2316,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2333,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572465</v>
+        <v>572482</v>
       </c>
       <c r="R17" t="n">
-        <v>6447034</v>
+        <v>6447052</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2393,6 +2395,209 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132698660</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>A 698, Öjsjön,Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>572501</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6447034</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131600750</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Brunstmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>572517</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6447054</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 698-2026 artfynd.xlsx
+++ b/artfynd/A 698-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109036973</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132696760</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131621114</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131600604</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131600466</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1317,6 +1347,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082418</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1427,6 +1462,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132696800</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1536,6 +1576,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982543</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1641,6 +1686,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982594</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1759,6 +1809,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082405</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1860,6 +1915,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131628992</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1967,6 +2027,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131600587</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2073,6 +2138,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132696822</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2179,6 +2249,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132696836</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2285,6 +2360,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132696862</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2395,6 +2475,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698650</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2501,6 +2586,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698660</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,8 +2688,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131600750</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>